--- a/public/exports-from-60/65120119.xlsx
+++ b/public/exports-from-60/65120119.xlsx
@@ -59,7 +59,7 @@
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Areal (m²)</t>
+          <t xml:space="preserve">Opvarmet BBR-areal (m²)</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
@@ -4264,7 +4264,7 @@
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t xml:space="preserve">311590114</t>
+          <t xml:space="preserve">311590119</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
@@ -10489,12 +10489,12 @@
       </c>
       <c r="K140" t="inlineStr">
         <is>
-          <t xml:space="preserve">311798611</t>
+          <t xml:space="preserve">311798613</t>
         </is>
       </c>
       <c r="L140" t="inlineStr">
         <is>
-          <t xml:space="preserve">GH-Energi &amp; Rådgivning ApS</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M140" t="inlineStr">

--- a/public/exports-from-60/65120119.xlsx
+++ b/public/exports-from-60/65120119.xlsx
@@ -4339,7 +4339,7 @@
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t xml:space="preserve">311590119</t>
+          <t xml:space="preserve">311590120</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
@@ -4414,7 +4414,7 @@
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t xml:space="preserve">311590119</t>
+          <t xml:space="preserve">311590120</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">

--- a/public/exports-from-60/65120119.xlsx
+++ b/public/exports-from-60/65120119.xlsx
@@ -4264,7 +4264,7 @@
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t xml:space="preserve">311590119</t>
+          <t xml:space="preserve">311590114</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
@@ -4339,7 +4339,7 @@
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t xml:space="preserve">311590120</t>
+          <t xml:space="preserve">311590119</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
@@ -4414,7 +4414,7 @@
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t xml:space="preserve">311590120</t>
+          <t xml:space="preserve">311590119</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
@@ -10489,12 +10489,12 @@
       </c>
       <c r="K140" t="inlineStr">
         <is>
-          <t xml:space="preserve">311798613</t>
+          <t xml:space="preserve">311798611</t>
         </is>
       </c>
       <c r="L140" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">GH-Energi &amp; Rådgivning ApS</t>
         </is>
       </c>
       <c r="M140" t="inlineStr">
